--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>c</t>
   </si>
@@ -32,12 +32,33 @@
   <si>
     <t>int</t>
   </si>
+  <si>
+    <t>通知客户端类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>oticeClientType</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +84,14 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,13 +120,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -402,41 +432,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:C9"/>
+  <dimension ref="B3:D9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -444,7 +484,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,6 +495,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>c</t>
   </si>
@@ -51,6 +51,63 @@
       </rPr>
       <t>oticeClientType</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总时长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[]</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tick间隔时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TickTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TickAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveAction</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -432,51 +489,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:D9"/>
+  <dimension ref="B3:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -484,7 +591,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="2:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>c</t>
   </si>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>RemoveAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff自身特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnerEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -489,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I9"/>
+  <dimension ref="B3:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -501,10 +513,11 @@
     <col min="7" max="7" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="10" max="10" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
@@ -526,8 +539,11 @@
       <c r="I3" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
@@ -549,8 +565,11 @@
       <c r="I4" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
@@ -572,18 +591,21 @@
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="6" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -591,7 +613,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -19,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -501,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:J9"/>
+  <dimension ref="C3:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -517,110 +511,107 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
+      <c r="J4" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3" t="s">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
+      <c r="E6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="1">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="1">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1004</v>
-      </c>
-    </row>
+    <row r="7" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -116,12 +116,114 @@
     <t>OwnerEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>备注说明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#野蛮冲撞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋状态，靠近的敌人会被击飞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋被击装填，无法移动和释放技能</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋状态，靠近的敌人会被击飞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10058,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10060</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10058</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10060</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +258,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -183,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -191,6 +300,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -495,123 +607,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:J9"/>
+  <dimension ref="B2:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="30" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>2001</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>1000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>1002</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>1002</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="1">
+        <v>30016</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <v>30017</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>30018</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10055</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10055</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
